--- a/Jal Rekha CMMIL5 Artefacts/new Cycle 4 Jan26 May26/Managing Performance & Measurement/Jal Rekha Data collection Cycle 4 _V_6.xlsx
+++ b/Jal Rekha CMMIL5 Artefacts/new Cycle 4 Jan26 May26/Managing Performance & Measurement/Jal Rekha Data collection Cycle 4 _V_6.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\MPSeDC MPSSDI GIS\Jal Rekha CMMIL5 Artefacts\new Cycle 4 Jan26 May26\Managing Performance &amp; Measurement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Projects\BusinessDataAnalysis_EngineeringRepo\Jal Rekha CMMIL5 Artefacts\new Cycle 4 Jan26 May26\Managing Performance &amp; Measurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
     <definedName name="MY_FUNCTION1" localSheetId="1">LAMBDA(((#REF!-#REF!)/#REF!)+1)</definedName>
     <definedName name="MY_FUNCTION1">LAMBDA(((#REF!-#REF!)/#REF!)+1)</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -579,32 +579,6 @@
   </si>
   <si>
     <t>Change Request FHTC GM - Contractor - Reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Customized &amp; Summary report corrections requirement 
-2. Handled changes in FHTC module and prepared related reports.
-3. API Creation in FHTC Module in Mobile &amp; Web for GM Login
-4. FHTC Internal Testing &amp; Bug Re-testing
-5. Modified Excel export in Jal Nigam Portal by updating dynamic file name, sheet name, header title as per module and hiding non-export columns (Action-Image-Document).
-6. Parinam Report Issue Analysis &amp; Fixing
-7. Create a new database function and API endpoint for contractor login.
-8. FHTC Loop functionality implementation
-9. As per change request FHTC Loop functionality implementation in Mobile and PIU Side &amp; in Reports
-10. As per change request FHTC Loop functionality implementation in SQC And TPIA  Side (Review)
-11. Work on Report Filter issues at column level for GM - Contractor Reports
-12. FHTC Module - UI enhancement. 
-13. FHTC- Add Loop(Re- Inspection) functionality for contractor login. 
-14. FHTC Module – History Screen, Accepted List, Rejected List &amp; Re-Inspection Form UI Design with API Integration.
-15. FHTC Module – Re-Inspection Form UI Design and API Data Submission.
-16. FHTC Module- FE login History screen and sync changes.
-17. FHTC – Re-Inspection List Screen Implementation &amp; API Integration for Field Engineer Login.
-18. FHTC – Re-Inspection List Screen Implementation &amp; API Integration for Field Engineer Login.
-19. FHTC Module – Re-Inspection Form UI Design and API Data Submission for FE.
-As per Change request FHTC Loop functionality implementation.
-20. FHTC Change request add View Logs functionality.
-21. FHTC Change request add on search functionality.
-22. FHTC Change request - Add Search Functionality to FE and Contractor login.
-</t>
   </si>
   <si>
     <t xml:space="preserve">1. Dhara Reports Validate (Scheme &amp; OHT &amp; Bulk Consumer)
@@ -765,6 +739,32 @@
 5. Test Case/Scenarios Creation for New Changes
 6. Issue : Data Not Loading Issue in WTP Meter Survey Page
 7. work on change request for bulk consumer meter reading
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Customized &amp; Summary report corrections requirement 
+2. Handled changes in FHTC module and prepared related reports.
+3. API Creation in FHTC Module in Mobile &amp; Web for GM Login
+4. FHTC Internal Testing &amp; Bug Re-testing
+5. Modified Excel export in Jal Nigam Portal by updating dynamic file name, sheet name, header title as per module and hiding non-export columns (Action-Image-Document) history screen changes
+6. Parinam Report Issue Analysis &amp; Fixing of FE los changes
+7. Create a new database function and API endpoint for contractor login.
+8. FHTC Loop functionality implementation
+9. As per change request FHTC Loop functionality implementation in Mobile and PIU Side &amp; in Reports
+10. As per change request FHTC Loop functionality implementation in SQC And TPIA  Side (Review)
+11. Work on Report Filter issues at column level for GM - Contractor Reports
+12. FHTC Module - UI enhancement. 
+13. FHTC- Add Loop(Re- Inspection) functionality for contractor login. 
+14. FHTC Module – History Screen, Accepted List, Rejected List &amp; Re-Inspection Form UI Design with API Integration.
+15. FHTC Module – Re-Inspection Form UI Design and API Data Submission.
+16. FHTC Module- FE login History screen and sync changes.
+17. FHTC – Re-Inspection List Screen Implementation &amp; API Integration for Field Engineer Login.
+18. FHTC – Re-Inspection List Screen Implementation &amp; API Integration for Field Engineer Login.
+19. FHTC Module – Re-Inspection Form UI Design and API Data Submission for FE.
+As per Change request FHTC Loop functionality implementation.
+20. FHTC Change request add View Logs functionality.
+21. FHTC Change request add on search functionality.
+22. FHTC Change request - Add Search Functionality to FE and Contractor login.
 </t>
   </si>
 </sst>
@@ -1532,6 +1532,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1545,12 +1551,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2862,7 +2862,7 @@
       <c r="C2" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="135" t="s">
+      <c r="D2" s="137" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="49" t="s">
@@ -3025,7 +3025,7 @@
       <c r="A3" s="45"/>
       <c r="B3" s="45"/>
       <c r="C3" s="45"/>
-      <c r="D3" s="136"/>
+      <c r="D3" s="138"/>
       <c r="E3" s="129" t="s">
         <v>84</v>
       </c>
@@ -3363,11 +3363,11 @@
       <c r="C5" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="135" t="s">
+      <c r="D5" s="137" t="s">
         <v>57</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F5" s="90" t="s">
         <v>108</v>
@@ -3526,12 +3526,12 @@
       <c r="A6" s="45"/>
       <c r="B6" s="45"/>
       <c r="C6" s="45"/>
-      <c r="D6" s="136"/>
+      <c r="D6" s="138"/>
       <c r="E6" s="129" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F6" s="90" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G6" s="45" t="s">
         <v>85</v>
@@ -3695,7 +3695,7 @@
       <c r="C7" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="135" t="s">
+      <c r="D7" s="137" t="s">
         <v>87</v>
       </c>
       <c r="E7" s="56" t="s">
@@ -3858,7 +3858,7 @@
       <c r="A8" s="45"/>
       <c r="B8" s="45"/>
       <c r="C8" s="45"/>
-      <c r="D8" s="137"/>
+      <c r="D8" s="139"/>
       <c r="E8" s="56" t="s">
         <v>55</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="A9" s="45"/>
       <c r="B9" s="45"/>
       <c r="C9" s="45"/>
-      <c r="D9" s="137"/>
+      <c r="D9" s="139"/>
       <c r="E9" s="56" t="s">
         <v>124</v>
       </c>
@@ -4180,7 +4180,7 @@
       <c r="A10" s="45"/>
       <c r="B10" s="45"/>
       <c r="C10" s="45"/>
-      <c r="D10" s="136"/>
+      <c r="D10" s="138"/>
       <c r="E10" s="56" t="s">
         <v>5</v>
       </c>
@@ -4341,14 +4341,14 @@
       <c r="A11" s="45"/>
       <c r="B11" s="45"/>
       <c r="C11" s="45"/>
-      <c r="D11" s="135" t="s">
+      <c r="D11" s="137" t="s">
         <v>89</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F11" s="90" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G11" s="45"/>
       <c r="H11" s="45">
@@ -4510,9 +4510,9 @@
       <c r="C12" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="137"/>
+      <c r="D12" s="139"/>
       <c r="E12" s="49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F12" s="90" t="s">
         <v>126</v>
@@ -4671,9 +4671,9 @@
       <c r="A13" s="82"/>
       <c r="B13" s="82"/>
       <c r="C13" s="82"/>
-      <c r="D13" s="137"/>
+      <c r="D13" s="139"/>
       <c r="E13" s="65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F13" s="95" t="s">
         <v>127</v>
@@ -4847,7 +4847,7 @@
         <v>128</v>
       </c>
       <c r="F14" s="115" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G14" s="112" t="s">
         <v>85</v>
@@ -5018,7 +5018,7 @@
         <v>91</v>
       </c>
       <c r="F15" s="101" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G15" s="83" t="s">
         <v>85</v>
@@ -5173,16 +5173,16 @@
       </c>
     </row>
     <row r="16" spans="1:52" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="138">
+      <c r="A16" s="133">
         <v>9</v>
       </c>
-      <c r="B16" s="138" t="s">
+      <c r="B16" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="138" t="s">
+      <c r="C16" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="139" t="s">
+      <c r="D16" s="134" t="s">
         <v>92</v>
       </c>
       <c r="E16" s="60" t="s">
@@ -5342,15 +5342,15 @@
       </c>
     </row>
     <row r="17" spans="1:52" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="138"/>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="139"/>
+      <c r="A17" s="133"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="134"/>
       <c r="E17" s="60" t="s">
         <v>93</v>
       </c>
       <c r="F17" s="90" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G17" s="45"/>
       <c r="H17" s="45">
@@ -5519,7 +5519,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G18" s="45" t="s">
         <v>85</v>
@@ -5683,7 +5683,7 @@
       <c r="C19" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="133" t="s">
+      <c r="D19" s="135" t="s">
         <v>94</v>
       </c>
       <c r="E19" s="62" t="s">
@@ -5848,12 +5848,12 @@
       <c r="A20" s="45"/>
       <c r="B20" s="45"/>
       <c r="C20" s="45"/>
-      <c r="D20" s="133"/>
+      <c r="D20" s="135"/>
       <c r="E20" s="62" t="s">
         <v>96</v>
       </c>
       <c r="F20" s="90" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G20" s="45" t="s">
         <v>85</v>
@@ -6011,7 +6011,7 @@
       <c r="A21" s="45"/>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
-      <c r="D21" s="134"/>
+      <c r="D21" s="136"/>
       <c r="E21" s="130" t="s">
         <v>97</v>
       </c>
@@ -6889,15 +6889,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D10"/>
+    <mergeCell ref="D11:D13"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="D19:D21"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="D11:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7186,7 +7186,7 @@
         <v>78</v>
       </c>
       <c r="O30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="15:18" x14ac:dyDescent="0.35">
@@ -8158,7 +8158,7 @@
         <v>78</v>
       </c>
       <c r="Q30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="16:19" x14ac:dyDescent="0.35">
@@ -9371,7 +9371,7 @@
         <v>78</v>
       </c>
       <c r="P30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="14:16" x14ac:dyDescent="0.35">

--- a/Jal Rekha CMMIL5 Artefacts/new Cycle 4 Jan26 May26/Managing Performance & Measurement/Jal Rekha Data collection Cycle 4 _V_6.xlsx
+++ b/Jal Rekha CMMIL5 Artefacts/new Cycle 4 Jan26 May26/Managing Performance & Measurement/Jal Rekha Data collection Cycle 4 _V_6.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DC JantoMay" sheetId="34" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="MY_FUNCTION1" localSheetId="1">LAMBDA(((#REF!-#REF!)/#REF!)+1)</definedName>
     <definedName name="MY_FUNCTION1">LAMBDA(((#REF!-#REF!)/#REF!)+1)</definedName>
   </definedNames>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -988,7 +988,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1144,30 +1144,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1178,7 +1154,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1492,18 +1468,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1532,6 +1496,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1543,15 +1516,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1563,7 +1527,18 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Percent 2" xfId="3"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1696,13 +1671,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>3</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>58702</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>57783</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2809,22 +2784,22 @@
         <v>35</v>
       </c>
       <c r="AL1" s="118"/>
-      <c r="AM1" s="123" t="s">
+      <c r="AM1" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="AN1" s="124" t="s">
+      <c r="AN1" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="124" t="s">
+      <c r="AO1" s="120" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="124" t="s">
+      <c r="AP1" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="124" t="s">
+      <c r="AQ1" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="125" t="s">
+      <c r="AR1" s="121" t="s">
         <v>42</v>
       </c>
       <c r="AS1" s="72" t="s">
@@ -2839,7 +2814,7 @@
       <c r="AV1" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="126" t="s">
+      <c r="AW1" s="122" t="s">
         <v>37</v>
       </c>
       <c r="AX1" s="72" t="s">
@@ -2862,7 +2837,7 @@
       <c r="C2" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="137" t="s">
+      <c r="D2" s="129" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="49" t="s">
@@ -2963,7 +2938,9 @@
       <c r="AK2" s="46">
         <v>0</v>
       </c>
-      <c r="AL2" s="119"/>
+      <c r="AL2">
+        <v>0.18333333333333332</v>
+      </c>
       <c r="AM2" s="117">
         <f>H2/I2</f>
         <v>0.18333333333333332</v>
@@ -3012,11 +2989,11 @@
         <f>AH2/H2</f>
         <v>4.5454545454545456E-2</v>
       </c>
-      <c r="AY2" s="127">
+      <c r="AY2" s="123">
         <f>(AF2+AH2+AG2)/H2</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="AZ2" s="127">
+      <c r="AZ2" s="123">
         <f>(AI2)/H2</f>
         <v>4.5454545454545456E-2</v>
       </c>
@@ -3025,8 +3002,8 @@
       <c r="A3" s="45"/>
       <c r="B3" s="45"/>
       <c r="C3" s="45"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="129" t="s">
+      <c r="D3" s="130"/>
+      <c r="E3" s="125" t="s">
         <v>84</v>
       </c>
       <c r="F3" s="90" t="s">
@@ -3114,7 +3091,7 @@
       <c r="AG3" s="46">
         <v>1</v>
       </c>
-      <c r="AH3" s="131">
+      <c r="AH3" s="127">
         <v>1</v>
       </c>
       <c r="AI3" s="46">
@@ -3126,7 +3103,9 @@
       <c r="AK3" s="46">
         <v>0</v>
       </c>
-      <c r="AL3" s="119"/>
+      <c r="AL3">
+        <v>0.19047619047619047</v>
+      </c>
       <c r="AM3" s="117">
         <f t="shared" ref="AM3:AM29" si="1">H3/I3</f>
         <v>0.19047619047619047</v>
@@ -3167,7 +3146,7 @@
         <f t="shared" ref="AV3:AV23" si="10">((W3-V3)/H3)</f>
         <v>0.25</v>
       </c>
-      <c r="AW3" s="128">
+      <c r="AW3" s="124">
         <f t="shared" ref="AW3:AW23" si="11">AY3/(AY3+AZ3)</f>
         <v>1</v>
       </c>
@@ -3175,11 +3154,11 @@
         <f t="shared" ref="AX3:AX23" si="12">AH3/H3</f>
         <v>0.25</v>
       </c>
-      <c r="AY3" s="127">
+      <c r="AY3" s="123">
         <f t="shared" ref="AY3:AY23" si="13">(AF3+AH3+AG3)/H3</f>
         <v>0.5</v>
       </c>
-      <c r="AZ3" s="127">
+      <c r="AZ3" s="123">
         <f t="shared" ref="AZ3:AZ23" si="14">(AI3)/H3</f>
         <v>0</v>
       </c>
@@ -3295,7 +3274,9 @@
       <c r="AK4" s="46">
         <v>0</v>
       </c>
-      <c r="AL4" s="119"/>
+      <c r="AL4">
+        <v>0.2</v>
+      </c>
       <c r="AM4" s="117">
         <f t="shared" si="1"/>
         <v>0.2</v>
@@ -3344,11 +3325,11 @@
         <f t="shared" si="12"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AY4" s="127">
+      <c r="AY4" s="123">
         <f t="shared" si="13"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AZ4" s="127">
+      <c r="AZ4" s="123">
         <f t="shared" si="14"/>
         <v>0.1111111111111111</v>
       </c>
@@ -3363,7 +3344,7 @@
       <c r="C5" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="137" t="s">
+      <c r="D5" s="129" t="s">
         <v>57</v>
       </c>
       <c r="E5" s="56" t="s">
@@ -3464,7 +3445,9 @@
       <c r="AK5" s="46">
         <v>1</v>
       </c>
-      <c r="AL5" s="119"/>
+      <c r="AL5">
+        <v>0.17948717948717949</v>
+      </c>
       <c r="AM5" s="117">
         <f t="shared" si="1"/>
         <v>0.17948717948717949</v>
@@ -3513,11 +3496,11 @@
         <f t="shared" si="12"/>
         <v>7.1428571428571425E-2</v>
       </c>
-      <c r="AY5" s="127">
+      <c r="AY5" s="123">
         <f t="shared" si="13"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AZ5" s="127">
+      <c r="AZ5" s="123">
         <f t="shared" si="14"/>
         <v>7.1428571428571425E-2</v>
       </c>
@@ -3526,8 +3509,8 @@
       <c r="A6" s="45"/>
       <c r="B6" s="45"/>
       <c r="C6" s="45"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="129" t="s">
+      <c r="D6" s="130"/>
+      <c r="E6" s="125" t="s">
         <v>134</v>
       </c>
       <c r="F6" s="90" t="s">
@@ -3612,7 +3595,7 @@
       <c r="AF6" s="46">
         <v>0</v>
       </c>
-      <c r="AG6" s="131">
+      <c r="AG6" s="127">
         <v>1</v>
       </c>
       <c r="AH6" s="46">
@@ -3627,7 +3610,9 @@
       <c r="AK6" s="46">
         <v>0</v>
       </c>
-      <c r="AL6" s="119"/>
+      <c r="AL6">
+        <v>0.18367346938775511</v>
+      </c>
       <c r="AM6" s="117">
         <f t="shared" si="1"/>
         <v>0.18367346938775511</v>
@@ -3668,7 +3653,7 @@
         <f t="shared" si="10"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AW6" s="128">
+      <c r="AW6" s="124">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -3676,11 +3661,11 @@
         <f t="shared" si="12"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AY6" s="127">
+      <c r="AY6" s="123">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="AZ6" s="127">
+      <c r="AZ6" s="123">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -3695,7 +3680,7 @@
       <c r="C7" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="137" t="s">
+      <c r="D7" s="129" t="s">
         <v>87</v>
       </c>
       <c r="E7" s="56" t="s">
@@ -3796,7 +3781,9 @@
       <c r="AK7" s="46">
         <v>2</v>
       </c>
-      <c r="AL7" s="119"/>
+      <c r="AL7">
+        <v>0.1875</v>
+      </c>
       <c r="AM7" s="117">
         <f t="shared" si="1"/>
         <v>0.1875</v>
@@ -3845,11 +3832,11 @@
         <f t="shared" si="12"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="AY7" s="127">
+      <c r="AY7" s="123">
         <f t="shared" si="13"/>
         <v>0.41666666666666669</v>
       </c>
-      <c r="AZ7" s="127">
+      <c r="AZ7" s="123">
         <f t="shared" si="14"/>
         <v>0.25</v>
       </c>
@@ -3858,7 +3845,7 @@
       <c r="A8" s="45"/>
       <c r="B8" s="45"/>
       <c r="C8" s="45"/>
-      <c r="D8" s="139"/>
+      <c r="D8" s="131"/>
       <c r="E8" s="56" t="s">
         <v>55</v>
       </c>
@@ -3957,7 +3944,9 @@
       <c r="AK8" s="46">
         <v>2</v>
       </c>
-      <c r="AL8" s="119"/>
+      <c r="AL8">
+        <v>0.18235294117647058</v>
+      </c>
       <c r="AM8" s="117">
         <f t="shared" si="1"/>
         <v>0.18235294117647058</v>
@@ -4006,11 +3995,11 @@
         <f t="shared" si="12"/>
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="AY8" s="127">
+      <c r="AY8" s="123">
         <f t="shared" si="13"/>
         <v>0.25806451612903225</v>
       </c>
-      <c r="AZ8" s="127">
+      <c r="AZ8" s="123">
         <f t="shared" si="14"/>
         <v>9.6774193548387094E-2</v>
       </c>
@@ -4019,7 +4008,7 @@
       <c r="A9" s="45"/>
       <c r="B9" s="45"/>
       <c r="C9" s="45"/>
-      <c r="D9" s="139"/>
+      <c r="D9" s="131"/>
       <c r="E9" s="56" t="s">
         <v>124</v>
       </c>
@@ -4118,7 +4107,9 @@
       <c r="AK9" s="46">
         <v>0</v>
       </c>
-      <c r="AL9" s="119"/>
+      <c r="AL9">
+        <v>0.17948717948717949</v>
+      </c>
       <c r="AM9" s="117">
         <f t="shared" si="1"/>
         <v>0.17948717948717949</v>
@@ -4167,11 +4158,11 @@
         <f t="shared" si="12"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AY9" s="127">
+      <c r="AY9" s="123">
         <f t="shared" si="13"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AZ9" s="127">
+      <c r="AZ9" s="123">
         <f t="shared" si="14"/>
         <v>0.14285714285714285</v>
       </c>
@@ -4180,7 +4171,7 @@
       <c r="A10" s="45"/>
       <c r="B10" s="45"/>
       <c r="C10" s="45"/>
-      <c r="D10" s="138"/>
+      <c r="D10" s="130"/>
       <c r="E10" s="56" t="s">
         <v>5</v>
       </c>
@@ -4279,7 +4270,9 @@
       <c r="AK10" s="46">
         <v>0</v>
       </c>
-      <c r="AL10" s="119"/>
+      <c r="AL10">
+        <v>0.17910447761194029</v>
+      </c>
       <c r="AM10" s="117">
         <f t="shared" si="1"/>
         <v>0.17910447761194029</v>
@@ -4328,11 +4321,11 @@
         <f t="shared" si="12"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AY10" s="127">
+      <c r="AY10" s="123">
         <f t="shared" si="13"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="AZ10" s="127">
+      <c r="AZ10" s="123">
         <f t="shared" si="14"/>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -4341,7 +4334,7 @@
       <c r="A11" s="45"/>
       <c r="B11" s="45"/>
       <c r="C11" s="45"/>
-      <c r="D11" s="137" t="s">
+      <c r="D11" s="129" t="s">
         <v>89</v>
       </c>
       <c r="E11" s="49" t="s">
@@ -4442,7 +4435,9 @@
       <c r="AK11" s="46">
         <v>0</v>
       </c>
-      <c r="AL11" s="119"/>
+      <c r="AL11">
+        <v>0.18681318681318682</v>
+      </c>
       <c r="AM11" s="117">
         <f t="shared" si="1"/>
         <v>0.18681318681318682</v>
@@ -4491,11 +4486,11 @@
         <f t="shared" si="12"/>
         <v>5.8823529411764705E-2</v>
       </c>
-      <c r="AY11" s="127">
+      <c r="AY11" s="123">
         <f t="shared" si="13"/>
         <v>5.8823529411764705E-2</v>
       </c>
-      <c r="AZ11" s="127">
+      <c r="AZ11" s="123">
         <f t="shared" si="14"/>
         <v>5.8823529411764705E-2</v>
       </c>
@@ -4510,7 +4505,7 @@
       <c r="C12" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="139"/>
+      <c r="D12" s="131"/>
       <c r="E12" s="49" t="s">
         <v>136</v>
       </c>
@@ -4609,7 +4604,9 @@
       <c r="AK12" s="46">
         <v>0</v>
       </c>
-      <c r="AL12" s="119"/>
+      <c r="AL12">
+        <v>0.18404907975460122</v>
+      </c>
       <c r="AM12" s="117">
         <f t="shared" si="1"/>
         <v>0.18404907975460122</v>
@@ -4658,11 +4655,11 @@
         <f t="shared" si="12"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="AY12" s="127">
+      <c r="AY12" s="123">
         <f t="shared" si="13"/>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="AZ12" s="127">
+      <c r="AZ12" s="123">
         <f t="shared" si="14"/>
         <v>3.3333333333333333E-2</v>
       </c>
@@ -4671,7 +4668,7 @@
       <c r="A13" s="82"/>
       <c r="B13" s="82"/>
       <c r="C13" s="82"/>
-      <c r="D13" s="139"/>
+      <c r="D13" s="131"/>
       <c r="E13" s="65" t="s">
         <v>135</v>
       </c>
@@ -4772,7 +4769,9 @@
       <c r="AK13" s="97">
         <v>0</v>
       </c>
-      <c r="AL13" s="120"/>
+      <c r="AL13">
+        <v>0.18220338983050846</v>
+      </c>
       <c r="AM13" s="117">
         <f t="shared" si="1"/>
         <v>0.18220338983050846</v>
@@ -4821,11 +4820,11 @@
         <f t="shared" si="12"/>
         <v>2.3255813953488372E-2</v>
       </c>
-      <c r="AY13" s="127">
+      <c r="AY13" s="123">
         <f t="shared" si="13"/>
         <v>4.6511627906976744E-2</v>
       </c>
-      <c r="AZ13" s="127">
+      <c r="AZ13" s="123">
         <f t="shared" si="14"/>
         <v>2.3255813953488372E-2</v>
       </c>
@@ -4943,7 +4942,9 @@
       <c r="AK14" s="116">
         <v>2</v>
       </c>
-      <c r="AL14" s="121"/>
+      <c r="AL14">
+        <v>0.17905405405405406</v>
+      </c>
       <c r="AM14" s="117">
         <f t="shared" si="1"/>
         <v>0.17905405405405406</v>
@@ -4992,11 +4993,11 @@
         <f t="shared" si="12"/>
         <v>3.7735849056603772E-2</v>
       </c>
-      <c r="AY14" s="127">
+      <c r="AY14" s="123">
         <f t="shared" si="13"/>
         <v>0.11320754716981132</v>
       </c>
-      <c r="AZ14" s="127">
+      <c r="AZ14" s="123">
         <f t="shared" si="14"/>
         <v>3.7735849056603772E-2</v>
       </c>
@@ -5114,7 +5115,9 @@
       <c r="AK15" s="102">
         <v>0</v>
       </c>
-      <c r="AL15" s="122"/>
+      <c r="AL15">
+        <v>0.18840579710144928</v>
+      </c>
       <c r="AM15" s="117">
         <f t="shared" si="1"/>
         <v>0.18095238095238095</v>
@@ -5163,26 +5166,26 @@
         <f t="shared" si="12"/>
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="AY15" s="127">
+      <c r="AY15" s="123">
         <f t="shared" si="13"/>
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="AZ15" s="127">
+      <c r="AZ15" s="123">
         <f t="shared" si="14"/>
         <v>2.6315789473684209E-2</v>
       </c>
     </row>
     <row r="16" spans="1:52" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="133">
+      <c r="A16" s="132">
         <v>9</v>
       </c>
-      <c r="B16" s="133" t="s">
+      <c r="B16" s="132" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="133" t="s">
+      <c r="C16" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="134" t="s">
+      <c r="D16" s="133" t="s">
         <v>92</v>
       </c>
       <c r="E16" s="60" t="s">
@@ -5283,7 +5286,9 @@
       <c r="AK16" s="46">
         <v>0</v>
       </c>
-      <c r="AL16" s="119"/>
+      <c r="AL16">
+        <v>0.18095238095238095</v>
+      </c>
       <c r="AM16" s="117">
         <f t="shared" si="1"/>
         <v>0.2</v>
@@ -5332,20 +5337,20 @@
         <f t="shared" si="12"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="AY16" s="127">
+      <c r="AY16" s="123">
         <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
-      <c r="AZ16" s="127">
+      <c r="AZ16" s="123">
         <f t="shared" si="14"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:52" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="133"/>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="134"/>
+      <c r="A17" s="132"/>
+      <c r="B17" s="132"/>
+      <c r="C17" s="132"/>
+      <c r="D17" s="133"/>
       <c r="E17" s="60" t="s">
         <v>93</v>
       </c>
@@ -5444,7 +5449,9 @@
       <c r="AK17" s="46">
         <v>2</v>
       </c>
-      <c r="AL17" s="119"/>
+      <c r="AL17">
+        <v>0.2</v>
+      </c>
       <c r="AM17" s="117">
         <f t="shared" si="1"/>
         <v>0.18</v>
@@ -5493,11 +5500,11 @@
         <f t="shared" si="12"/>
         <v>4.4444444444444446E-2</v>
       </c>
-      <c r="AY17" s="127">
+      <c r="AY17" s="123">
         <f t="shared" si="13"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AZ17" s="127">
+      <c r="AZ17" s="123">
         <f t="shared" si="14"/>
         <v>4.4444444444444446E-2</v>
       </c>
@@ -5615,7 +5622,9 @@
       <c r="AK18" s="46">
         <v>0</v>
       </c>
-      <c r="AL18" s="119"/>
+      <c r="AL18">
+        <v>0.18</v>
+      </c>
       <c r="AM18" s="117">
         <f t="shared" si="1"/>
         <v>0.17886178861788618</v>
@@ -5664,11 +5673,11 @@
         <f t="shared" si="12"/>
         <v>4.5454545454545456E-2</v>
       </c>
-      <c r="AY18" s="127">
+      <c r="AY18" s="123">
         <f t="shared" si="13"/>
         <v>4.5454545454545456E-2</v>
       </c>
-      <c r="AZ18" s="127">
+      <c r="AZ18" s="123">
         <f t="shared" si="14"/>
         <v>4.5454545454545456E-2</v>
       </c>
@@ -5683,7 +5692,7 @@
       <c r="C19" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="135" t="s">
+      <c r="D19" s="134" t="s">
         <v>94</v>
       </c>
       <c r="E19" s="62" t="s">
@@ -5786,7 +5795,9 @@
       <c r="AK19" s="46">
         <v>1</v>
       </c>
-      <c r="AL19" s="119"/>
+      <c r="AL19">
+        <v>0.17886178861788618</v>
+      </c>
       <c r="AM19" s="117">
         <f t="shared" si="1"/>
         <v>0.1796875</v>
@@ -5835,11 +5846,11 @@
         <f t="shared" si="12"/>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="AY19" s="127">
+      <c r="AY19" s="123">
         <f t="shared" si="13"/>
         <v>0.15217391304347827</v>
       </c>
-      <c r="AZ19" s="127">
+      <c r="AZ19" s="123">
         <f t="shared" si="14"/>
         <v>4.3478260869565216E-2</v>
       </c>
@@ -5848,7 +5859,7 @@
       <c r="A20" s="45"/>
       <c r="B20" s="45"/>
       <c r="C20" s="45"/>
-      <c r="D20" s="135"/>
+      <c r="D20" s="134"/>
       <c r="E20" s="62" t="s">
         <v>96</v>
       </c>
@@ -5949,7 +5960,9 @@
       <c r="AK20" s="46">
         <v>0</v>
       </c>
-      <c r="AL20" s="119"/>
+      <c r="AL20">
+        <v>0.1796875</v>
+      </c>
       <c r="AM20" s="117">
         <f t="shared" si="1"/>
         <v>0.18072289156626506</v>
@@ -5998,11 +6011,11 @@
         <f t="shared" si="12"/>
         <v>8.8888888888888892E-2</v>
       </c>
-      <c r="AY20" s="127">
+      <c r="AY20" s="123">
         <f t="shared" si="13"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="AZ20" s="127">
+      <c r="AZ20" s="123">
         <f t="shared" si="14"/>
         <v>4.4444444444444446E-2</v>
       </c>
@@ -6011,8 +6024,8 @@
       <c r="A21" s="45"/>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="130" t="s">
+      <c r="D21" s="135"/>
+      <c r="E21" s="126" t="s">
         <v>97</v>
       </c>
       <c r="F21" s="90" t="s">
@@ -6092,7 +6105,7 @@
       <c r="AE21" s="47">
         <v>0</v>
       </c>
-      <c r="AF21" s="131">
+      <c r="AF21" s="127">
         <v>1</v>
       </c>
       <c r="AG21" s="46">
@@ -6110,7 +6123,9 @@
       <c r="AK21" s="46">
         <v>0</v>
       </c>
-      <c r="AL21" s="119"/>
+      <c r="AL21">
+        <v>0.18072289156626506</v>
+      </c>
       <c r="AM21" s="117">
         <f t="shared" si="1"/>
         <v>0.19230769230769232</v>
@@ -6151,7 +6166,7 @@
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="AW21" s="128">
+      <c r="AW21" s="124">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -6159,11 +6174,11 @@
         <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="AY21" s="127">
+      <c r="AY21" s="123">
         <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
-      <c r="AZ21" s="127">
+      <c r="AZ21" s="123">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -6281,7 +6296,9 @@
       <c r="AK22" s="45">
         <v>0</v>
       </c>
-      <c r="AL22" s="55"/>
+      <c r="AL22">
+        <v>0.19230769230769232</v>
+      </c>
       <c r="AM22" s="117">
         <f t="shared" si="1"/>
         <v>0.18518518518518517</v>
@@ -6330,11 +6347,11 @@
         <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="AY22" s="127">
+      <c r="AY22" s="123">
         <f t="shared" si="13"/>
         <v>0.2</v>
       </c>
-      <c r="AZ22" s="127">
+      <c r="AZ22" s="123">
         <f t="shared" si="14"/>
         <v>0.1</v>
       </c>
@@ -6352,7 +6369,7 @@
       <c r="D23" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="129" t="s">
+      <c r="E23" s="125" t="s">
         <v>100</v>
       </c>
       <c r="F23" s="90" t="s">
@@ -6435,7 +6452,7 @@
       <c r="AF23" s="45">
         <v>0</v>
       </c>
-      <c r="AG23" s="131">
+      <c r="AG23" s="127">
         <v>1</v>
       </c>
       <c r="AH23" s="45">
@@ -6450,7 +6467,9 @@
       <c r="AK23" s="45">
         <v>0</v>
       </c>
-      <c r="AL23" s="55"/>
+      <c r="AL23">
+        <v>0.18518518518518517</v>
+      </c>
       <c r="AM23" s="117">
         <f t="shared" si="1"/>
         <v>0.18032786885245902</v>
@@ -6491,7 +6510,7 @@
         <f t="shared" si="10"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="AW23" s="128">
+      <c r="AW23" s="124">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -6499,17 +6518,20 @@
         <f t="shared" si="12"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="AY23" s="127">
+      <c r="AY23" s="123">
         <f t="shared" si="13"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="AZ23" s="127">
+      <c r="AZ23" s="123">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:52" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H24" s="48"/>
+      <c r="AL24">
+        <v>0.18032786885245902</v>
+      </c>
       <c r="AM24" s="103"/>
     </row>
     <row r="25" spans="1:52" ht="63" customHeight="1" x14ac:dyDescent="0.35">
@@ -6889,6 +6911,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="D19:D21"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D7:D10"/>
@@ -6897,8 +6920,10 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D19:D21"/>
   </mergeCells>
+  <conditionalFormatting sqref="AL1:AM1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6906,7 +6931,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -7065,310 +7090,299 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>0.18840579710144928</v>
+        <v>0.18095238095238095</v>
       </c>
       <c r="B15">
-        <v>0.31707317073170732</v>
+        <v>0.29457364341085274</v>
       </c>
       <c r="C15">
-        <v>0.8125</v>
+        <v>0.70370370370370372</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>0.18095238095238095</v>
+        <v>0.2</v>
       </c>
       <c r="B16">
-        <v>0.29457364341085274</v>
+        <v>0.31578947368421051</v>
       </c>
       <c r="C16">
-        <v>0.70370370370370372</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="B17">
-        <v>0.31578947368421051</v>
+        <v>0.32374100719424459</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.58441558441558439</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>0.18</v>
+        <v>0.17886178861788618</v>
       </c>
       <c r="B18">
-        <v>0.32374100719424459</v>
+        <v>0.3188405797101449</v>
       </c>
       <c r="C18">
-        <v>0.58441558441558439</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>0.17886178861788618</v>
+        <v>0.1796875</v>
       </c>
       <c r="B19">
-        <v>0.3188405797101449</v>
+        <v>0.31944444444444442</v>
       </c>
       <c r="C19">
-        <v>0.55000000000000004</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>0.1796875</v>
+        <v>0.18072289156626506</v>
       </c>
       <c r="B20">
-        <v>0.31944444444444442</v>
+        <v>0.31468531468531469</v>
       </c>
       <c r="C20">
-        <v>0.66666666666666663</v>
+        <v>0.67164179104477617</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>0.18072289156626506</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="B21">
-        <v>0.31468531468531469</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C21">
-        <v>0.67164179104477617</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>0.19230769230769232</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="B22">
-        <v>0.33333333333333331</v>
+        <v>0.30303030303030304</v>
       </c>
       <c r="C22">
-        <v>0.7142857142857143</v>
+        <v>0.58823529411764708</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>0.18518518518518517</v>
+        <v>0.18032786885245902</v>
       </c>
       <c r="B23">
-        <v>0.30303030303030304</v>
+        <v>0.2558139534883721</v>
       </c>
       <c r="C23">
-        <v>0.58823529411764708</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>0.18032786885245902</v>
-      </c>
-      <c r="B24">
-        <v>0.2558139534883721</v>
-      </c>
-      <c r="C24">
         <v>0.84615384615384615</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="M28" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="M29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="M30" t="s">
         <v>36</v>
       </c>
-      <c r="N30" t="s">
+      <c r="N29" t="s">
         <v>78</v>
       </c>
-      <c r="O30" t="s">
+      <c r="O29" t="s">
         <v>138</v>
       </c>
     </row>
+    <row r="35" spans="15:18" x14ac:dyDescent="0.35">
+      <c r="O35" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="R35" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="36" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O36" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="P36" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="R36" s="9" t="s">
-        <v>41</v>
+      <c r="O36" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P36" s="24">
+        <v>0.18452099999999999</v>
+      </c>
+      <c r="Q36" s="24">
+        <v>0.31447900000000001</v>
+      </c>
+      <c r="R36" s="24">
+        <v>0.72905200000000003</v>
       </c>
     </row>
     <row r="37" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O37" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="P37" s="24">
-        <v>0.18452099999999999</v>
-      </c>
-      <c r="Q37" s="24">
-        <v>0.31447900000000001</v>
-      </c>
-      <c r="R37" s="24">
-        <v>0.72905200000000003</v>
+        <v>61</v>
+      </c>
+      <c r="P37" s="18">
+        <f>(P38-P39)/6</f>
+        <v>3.0056166666666672E-2</v>
+      </c>
+      <c r="Q37" s="18">
+        <f t="shared" ref="Q37:R37" si="0">(Q38-Q39)/6</f>
+        <v>1.2762333333333339E-2</v>
+      </c>
+      <c r="R37" s="18">
+        <f t="shared" si="0"/>
+        <v>0.13390566666666667</v>
       </c>
     </row>
     <row r="38" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O38" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="P38" s="18">
-        <f>(P39-P40)/6</f>
-        <v>3.0056166666666672E-2</v>
-      </c>
-      <c r="Q38" s="18">
-        <f t="shared" ref="Q38:R38" si="0">(Q39-Q40)/6</f>
-        <v>1.2762333333333339E-2</v>
-      </c>
-      <c r="R38" s="18">
-        <f t="shared" si="0"/>
-        <v>0.13390566666666667</v>
+        <v>62</v>
+      </c>
+      <c r="P38" s="17">
+        <v>0.20283300000000001</v>
+      </c>
+      <c r="Q38" s="17">
+        <v>0.35276600000000002</v>
+      </c>
+      <c r="R38" s="17">
+        <v>1.1307700000000001</v>
       </c>
     </row>
     <row r="39" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O39" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P39" s="17">
-        <v>0.20283300000000001</v>
+        <v>2.2495999999999999E-2</v>
       </c>
       <c r="Q39" s="17">
-        <v>0.35276600000000002</v>
+        <v>0.27619199999999999</v>
       </c>
       <c r="R39" s="17">
-        <v>1.1307700000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O40" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="P40" s="17">
-        <v>2.2495999999999999E-2</v>
-      </c>
-      <c r="Q40" s="17">
-        <v>0.27619199999999999</v>
-      </c>
-      <c r="R40" s="17">
         <v>0.32733600000000002</v>
       </c>
     </row>
+    <row r="41" spans="15:18" x14ac:dyDescent="0.35">
+      <c r="O41" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P41" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13"/>
+    </row>
     <row r="42" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O42" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="P42" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q42" s="13"/>
-      <c r="R42" s="13"/>
+      <c r="O42" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P42" s="19">
+        <f>P36+R42</f>
+        <v>0.20297309999999999</v>
+      </c>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="13">
+        <f>P36*10%</f>
+        <v>1.8452099999999999E-2</v>
+      </c>
     </row>
     <row r="43" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O43" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="P43" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="13"/>
+    </row>
+    <row r="45" spans="15:18" x14ac:dyDescent="0.35">
+      <c r="O45" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="P45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q45" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="R45" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="15:18" x14ac:dyDescent="0.35">
+      <c r="O46" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="P43" s="19">
-        <f>P37+R43</f>
-        <v>0.20297309999999999</v>
-      </c>
-      <c r="Q43" s="14"/>
-      <c r="R43" s="13">
-        <f>P37*10%</f>
-        <v>1.8452099999999999E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O44" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="P44" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="Q44" s="13"/>
-      <c r="R44" s="13"/>
-    </row>
-    <row r="46" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O46" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="P46" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q46" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="R46" s="9" t="s">
-        <v>41</v>
+      <c r="P46" s="15">
+        <f>0.1199 + (0.1236*Q46) + (0.0354*R46)</f>
+        <v>0.19943000000000002</v>
+      </c>
+      <c r="Q46" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="R46" s="22">
+        <v>0.85</v>
       </c>
     </row>
     <row r="47" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O47" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="P47" s="15">
-        <f>0.1199 + (0.1236*Q47) + (0.0354*R47)</f>
-        <v>0.19943000000000002</v>
-      </c>
-      <c r="Q47" s="22">
-        <v>0.4</v>
-      </c>
-      <c r="R47" s="22">
-        <v>0.85</v>
+        <v>61</v>
+      </c>
+      <c r="P47" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="Q47" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="R47" s="18">
+        <v>0.05</v>
       </c>
     </row>
     <row r="48" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O48" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="P48" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="Q48" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="R48" s="18">
-        <v>0.05</v>
+        <v>66</v>
+      </c>
+      <c r="P48" s="10">
+        <f>P46+(3*P47)</f>
+        <v>0.34943000000000002</v>
+      </c>
+      <c r="Q48" s="10">
+        <f t="shared" ref="Q48:R48" si="1">Q46+(3*Q47)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R48" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="15:18" x14ac:dyDescent="0.35">
       <c r="O49" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P49" s="10">
-        <f>P47+(3*P48)</f>
-        <v>0.34943000000000002</v>
+        <f>P46-(3*P47)</f>
+        <v>4.9430000000000002E-2</v>
       </c>
       <c r="Q49" s="10">
-        <f t="shared" ref="Q49:R49" si="1">Q47+(3*Q48)</f>
-        <v>0.55000000000000004</v>
+        <f t="shared" ref="Q49:R49" si="2">Q46-(3*Q47)</f>
+        <v>0.25</v>
       </c>
       <c r="R49" s="10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O50" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="P50" s="10">
-        <f>P47-(3*P48)</f>
-        <v>4.9430000000000002E-2</v>
-      </c>
-      <c r="Q50" s="10">
-        <f t="shared" ref="Q50:R50" si="2">Q47-(3*Q48)</f>
-        <v>0.25</v>
-      </c>
-      <c r="R50" s="10">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
@@ -9175,186 +9189,186 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="132" t="s">
+      <c r="B1" s="128" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="132">
+      <c r="A2" s="128">
         <v>0.66666666666666674</v>
       </c>
-      <c r="B2" s="132">
+      <c r="B2" s="128">
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="132">
-        <v>1</v>
-      </c>
-      <c r="B3" s="132">
+      <c r="A3" s="128">
+        <v>1</v>
+      </c>
+      <c r="B3" s="128">
         <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="132">
+      <c r="A4" s="128">
         <v>0.5</v>
       </c>
-      <c r="B4" s="132">
+      <c r="B4" s="128">
         <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="132">
+      <c r="A5" s="128">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B5" s="132">
+      <c r="B5" s="128">
         <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="132">
-        <v>1</v>
-      </c>
-      <c r="B6" s="132">
+      <c r="A6" s="128">
+        <v>1</v>
+      </c>
+      <c r="B6" s="128">
         <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="132">
+      <c r="A7" s="128">
         <v>0.625</v>
       </c>
-      <c r="B7" s="132">
+      <c r="B7" s="128">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="132">
+      <c r="A8" s="128">
         <v>0.72727272727272718</v>
       </c>
-      <c r="B8" s="132">
+      <c r="B8" s="128">
         <v>9.6774193548387094E-2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="132">
+      <c r="A9" s="128">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B9" s="132">
+      <c r="B9" s="128">
         <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="132">
+      <c r="A10" s="128">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B10" s="132">
+      <c r="B10" s="128">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="132">
+      <c r="A11" s="128">
         <v>0.5</v>
       </c>
-      <c r="B11" s="132">
+      <c r="B11" s="128">
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="132">
+      <c r="A12" s="128">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B12" s="132">
+      <c r="B12" s="128">
         <v>3.3333333333333333E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="132">
+      <c r="A13" s="128">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B13" s="132">
+      <c r="B13" s="128">
         <v>2.3255813953488372E-2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="132">
+      <c r="A14" s="128">
         <v>0.75</v>
       </c>
-      <c r="B14" s="132">
+      <c r="B14" s="128">
         <v>3.7735849056603772E-2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="132">
+      <c r="A15" s="128">
         <v>0.5</v>
       </c>
-      <c r="B15" s="132">
+      <c r="B15" s="128">
         <v>2.6315789473684209E-2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="132">
+      <c r="A16" s="128">
         <v>0.75</v>
       </c>
-      <c r="B16" s="132">
+      <c r="B16" s="128">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="132">
+      <c r="A17" s="128">
         <v>0.71428571428571419</v>
       </c>
-      <c r="B17" s="132">
+      <c r="B17" s="128">
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="132">
+      <c r="A18" s="128">
         <v>0.5</v>
       </c>
-      <c r="B18" s="132">
+      <c r="B18" s="128">
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A19" s="132">
+      <c r="A19" s="128">
         <v>0.77777777777777779</v>
       </c>
-      <c r="B19" s="132">
+      <c r="B19" s="128">
         <v>8.6956521739130432E-2</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A20" s="132">
+      <c r="A20" s="128">
         <v>0.75</v>
       </c>
-      <c r="B20" s="132">
+      <c r="B20" s="128">
         <v>8.8888888888888892E-2</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="132">
-        <v>1</v>
-      </c>
-      <c r="B21" s="132">
+      <c r="A21" s="128">
+        <v>1</v>
+      </c>
+      <c r="B21" s="128">
         <v>0.2</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="132">
+      <c r="A22" s="128">
         <v>0.66666666666666663</v>
       </c>
-      <c r="B22" s="132">
+      <c r="B22" s="128">
         <v>0.2</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="132">
-        <v>1</v>
-      </c>
-      <c r="B23" s="132">
+      <c r="A23" s="128">
+        <v>1</v>
+      </c>
+      <c r="B23" s="128">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
